--- a/Resumo_atividade/Resumo-survey_os_20260908.xlsx
+++ b/Resumo_atividade/Resumo-survey_os_20260908.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="383">
   <si>
     <t>Número</t>
   </si>
@@ -52,84 +52,117 @@
     <t>Abertura</t>
   </si>
   <si>
+    <t>OS-2026-0124</t>
+  </si>
+  <si>
+    <t>Aberta</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Felipe Oliveira da Silva</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Avaré</t>
+  </si>
+  <si>
+    <t>Residencial Mario Emilio Banwart</t>
+  </si>
+  <si>
+    <t>Avenida Muntaha B. Urrea Lopes, 395</t>
+  </si>
+  <si>
+    <t>-23.106624, -48.888536</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>OS-2026-0122</t>
+  </si>
+  <si>
+    <t>Encerrada</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>-25.221782, -51.000775</t>
+  </si>
+  <si>
+    <t>PR (201 e 202)</t>
+  </si>
+  <si>
     <t>OS-2026-0121</t>
   </si>
   <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>Prudentópolis</t>
+  </si>
+  <si>
+    <t>Avenida São João</t>
+  </si>
+  <si>
+    <t>-25.221253, -50.998050</t>
+  </si>
+  <si>
+    <t>OS-2026-0120</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Rua Cornelio Kloster</t>
+  </si>
+  <si>
+    <t>-25.221372, -50.997958</t>
+  </si>
+  <si>
+    <t>OS-2026-0119</t>
+  </si>
+  <si>
+    <t>-25.221700, -50.997730</t>
+  </si>
+  <si>
+    <t>OS-2026-0118</t>
+  </si>
+  <si>
+    <t>-25.221952, -50.997563</t>
+  </si>
+  <si>
+    <t>OS-2026-0117</t>
+  </si>
+  <si>
+    <t>-25.222235, -50.997472</t>
+  </si>
+  <si>
+    <t>OS-2026-0116</t>
+  </si>
+  <si>
+    <t>Rua F</t>
+  </si>
+  <si>
+    <t>-25.222468, -50.997310</t>
+  </si>
+  <si>
+    <t>OS-2026-0115</t>
+  </si>
+  <si>
+    <t>-25.222530, -50.997230</t>
+  </si>
+  <si>
+    <t>OS-2026-0114</t>
+  </si>
+  <si>
     <t>Atribuída</t>
   </si>
   <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Ivan</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>Prudentópolis</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Avenida São João</t>
-  </si>
-  <si>
-    <t>-25.221253, -50.998050</t>
-  </si>
-  <si>
-    <t>PR (201 e 202)</t>
-  </si>
-  <si>
-    <t>OS-2026-0120</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>Rua Cornelio Kloster</t>
-  </si>
-  <si>
-    <t>-25.221372, -50.997958</t>
-  </si>
-  <si>
-    <t>OS-2026-0119</t>
-  </si>
-  <si>
-    <t>-25.221700, -50.997730</t>
-  </si>
-  <si>
-    <t>OS-2026-0118</t>
-  </si>
-  <si>
-    <t>-25.221952, -50.997563</t>
-  </si>
-  <si>
-    <t>OS-2026-0117</t>
-  </si>
-  <si>
-    <t>-25.222235, -50.997472</t>
-  </si>
-  <si>
-    <t>OS-2026-0116</t>
-  </si>
-  <si>
-    <t>Rua F</t>
-  </si>
-  <si>
-    <t>-25.222468, -50.997310</t>
-  </si>
-  <si>
-    <t>OS-2026-0115</t>
-  </si>
-  <si>
-    <t>-25.222530, -50.997230</t>
-  </si>
-  <si>
-    <t>OS-2026-0114</t>
-  </si>
-  <si>
     <t>Willian Henrique Freire de Carvalho</t>
   </si>
   <si>
@@ -178,9 +211,6 @@
     <t>Juliano Julio do Nascimento Silva</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
     <t>Carapicuiba</t>
   </si>
   <si>
@@ -229,9 +259,6 @@
     <t>OS-2026-0105</t>
   </si>
   <si>
-    <t>Encerrada</t>
-  </si>
-  <si>
     <t>Rua Capitão Francisco Durski Silva</t>
   </si>
   <si>
@@ -295,6 +322,9 @@
     <t>OS-2026-0097</t>
   </si>
   <si>
+    <t>Recebida</t>
+  </si>
+  <si>
     <t>Luiz Fernando Cardoso Montanheiro</t>
   </si>
   <si>
@@ -413,9 +443,6 @@
   </si>
   <si>
     <t>OS-2026-0086</t>
-  </si>
-  <si>
-    <t>Em deslocamento</t>
   </si>
   <si>
     <t>Alan Junior Nunes Pereira</t>
@@ -1528,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1617,13 +1644,13 @@
         <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L2" s="1">
         <v>46275.125</v>
       </c>
       <c r="M2" s="1">
-        <v>46273.57287974537</v>
+        <v>46273.78838958334</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -1631,614 +1658,614 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1">
         <v>46275.125</v>
       </c>
       <c r="M3" s="1">
-        <v>46273.57164863426</v>
+        <v>46273.697408761574</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
       </c>
       <c r="L4" s="1">
         <v>46275.125</v>
       </c>
       <c r="M4" s="1">
-        <v>46273.56904423611</v>
+        <v>46273.57287974537</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
         <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
       </c>
       <c r="L5" s="1">
         <v>46275.125</v>
       </c>
       <c r="M5" s="1">
-        <v>46273.565758171295</v>
+        <v>46273.57164863426</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" t="s">
         <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>16</v>
       </c>
       <c r="L6" s="1">
         <v>46275.125</v>
       </c>
       <c r="M6" s="1">
-        <v>46273.56331427083</v>
+        <v>46273.56904423611</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L7" s="1">
         <v>46275.125</v>
       </c>
       <c r="M7" s="1">
-        <v>46273.56011826389</v>
+        <v>46273.565758171295</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" t="s">
         <v>25</v>
-      </c>
-      <c r="I8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" t="s">
-        <v>16</v>
       </c>
       <c r="L8" s="1">
         <v>46275.125</v>
       </c>
       <c r="M8" s="1">
-        <v>46273.55643208334</v>
+        <v>46273.56331427083</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L9" s="1">
         <v>46275.125</v>
       </c>
       <c r="M9" s="1">
-        <v>46273.5543750463</v>
+        <v>46273.56011826389</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" t="s">
         <v>25</v>
-      </c>
-      <c r="I10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
-        <v>16</v>
       </c>
       <c r="L10" s="1">
         <v>46275.125</v>
       </c>
       <c r="M10" s="1">
-        <v>46273.552655810185</v>
+        <v>46273.55643208334</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="L11" s="1">
         <v>46275.125</v>
       </c>
       <c r="M11" s="1">
-        <v>46273.548741122686</v>
+        <v>46273.5543750463</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" t="s">
         <v>25</v>
-      </c>
-      <c r="I12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" t="s">
-        <v>16</v>
       </c>
       <c r="L12" s="1">
         <v>46275.125</v>
       </c>
       <c r="M12" s="1">
-        <v>46273.54481487269</v>
+        <v>46273.552655810185</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" t="s">
         <v>25</v>
-      </c>
-      <c r="I13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" t="s">
-        <v>16</v>
       </c>
       <c r="L13" s="1">
         <v>46275.125</v>
       </c>
       <c r="M13" s="1">
-        <v>46273.54172325232</v>
+        <v>46273.548741122686</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" t="s">
         <v>25</v>
-      </c>
-      <c r="I14" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" t="s">
-        <v>16</v>
       </c>
       <c r="L14" s="1">
         <v>46275.125</v>
       </c>
       <c r="M14" s="1">
-        <v>46273.54014961806</v>
+        <v>46273.54481487269</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="L15" s="1">
-        <v>46274.125</v>
+        <v>46275.125</v>
       </c>
       <c r="M15" s="1">
-        <v>46273.53019881944</v>
+        <v>46273.54172325232</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
         <v>61</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" t="s">
-        <v>65</v>
-      </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K16" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="L16" s="1">
         <v>46275.125</v>
       </c>
       <c r="M16" s="1">
-        <v>46273.51988820602</v>
+        <v>46273.54014961806</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s">
         <v>66</v>
       </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>67</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>68</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>69</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
         <v>70</v>
       </c>
-      <c r="J17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" t="s">
-        <v>60</v>
-      </c>
       <c r="L17" s="1">
-        <v>46275.125</v>
+        <v>46274.125</v>
       </c>
       <c r="M17" s="1">
-        <v>46273.5132640625</v>
+        <v>46273.53019881944</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -2246,368 +2273,368 @@
         <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
       </c>
       <c r="K18" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="L18" s="1">
-        <v>46274.125</v>
+        <v>46275.125</v>
       </c>
       <c r="M18" s="1">
-        <v>46272.768778206024</v>
+        <v>46273.51988820602</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
       </c>
       <c r="K19" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="L19" s="1">
-        <v>46274.125</v>
+        <v>46275.125</v>
       </c>
       <c r="M19" s="1">
-        <v>46272.766520034726</v>
+        <v>46273.5132640625</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H20" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J20" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L20" s="1">
         <v>46274.125</v>
       </c>
       <c r="M20" s="1">
-        <v>46272.765829791664</v>
+        <v>46272.768778206024</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H21" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I21" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L21" s="1">
         <v>46274.125</v>
       </c>
       <c r="M21" s="1">
-        <v>46272.76024550926</v>
+        <v>46272.766520034726</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L22" s="1">
         <v>46274.125</v>
       </c>
       <c r="M22" s="1">
-        <v>46272.75799625</v>
+        <v>46272.765829791664</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H23" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J23" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K23" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L23" s="1">
         <v>46274.125</v>
       </c>
       <c r="M23" s="1">
-        <v>46272.75278471065</v>
+        <v>46272.76024550926</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J24" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K24" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="L24" s="1">
         <v>46274.125</v>
       </c>
       <c r="M24" s="1">
-        <v>46272.69800121528</v>
+        <v>46272.75799625</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H25" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J25" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K25" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="L25" s="1">
         <v>46274.125</v>
       </c>
       <c r="M25" s="1">
-        <v>46272.69537929398</v>
+        <v>46272.75278471065</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="H26" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" t="s">
+        <v>99</v>
+      </c>
+      <c r="J26" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" t="s">
         <v>97</v>
       </c>
-      <c r="I26" t="s">
-        <v>98</v>
-      </c>
-      <c r="J26" t="s">
-        <v>22</v>
-      </c>
-      <c r="K26" t="s">
-        <v>99</v>
-      </c>
       <c r="L26" s="1">
-        <v>46272.125</v>
+        <v>46274.125</v>
       </c>
       <c r="M26" s="1">
-        <v>46272.66655380787</v>
+        <v>46272.69800121528</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -2615,409 +2642,409 @@
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" t="s">
         <v>101</v>
       </c>
-      <c r="H27" t="s">
-        <v>102</v>
-      </c>
-      <c r="I27" t="s">
-        <v>19</v>
-      </c>
       <c r="J27" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L27" s="1">
         <v>46274.125</v>
       </c>
       <c r="M27" s="1">
-        <v>46272.644796354165</v>
+        <v>46272.69537929398</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" t="s">
         <v>103</v>
-      </c>
-      <c r="B28" t="s">
-        <v>72</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K28" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="L28" s="1">
-        <v>46274.125</v>
+        <v>46272.125</v>
       </c>
       <c r="M28" s="1">
-        <v>46272.6127180787</v>
+        <v>46272.66655380787</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I29" t="s">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K29" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="L29" s="1">
         <v>46274.125</v>
       </c>
       <c r="M29" s="1">
-        <v>46272.61125947916</v>
+        <v>46272.644796354165</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H30" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J30" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K30" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L30" s="1">
         <v>46274.125</v>
       </c>
       <c r="M30" s="1">
-        <v>46272.6058525</v>
+        <v>46272.6127180787</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I31" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J31" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K31" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L31" s="1">
         <v>46274.125</v>
       </c>
       <c r="M31" s="1">
-        <v>46272.60366350695</v>
+        <v>46272.61125947916</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
         <v>15</v>
       </c>
       <c r="D32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" t="s">
         <v>114</v>
       </c>
-      <c r="E32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" t="s">
-        <v>115</v>
-      </c>
-      <c r="G32" t="s">
-        <v>116</v>
-      </c>
-      <c r="H32" t="s">
-        <v>117</v>
-      </c>
       <c r="I32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J32" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K32" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="L32" s="1">
         <v>46274.125</v>
       </c>
       <c r="M32" s="1">
-        <v>46272.59989282407</v>
+        <v>46272.6058525</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H33" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="I33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J33" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K33" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L33" s="1">
         <v>46274.125</v>
       </c>
       <c r="M33" s="1">
-        <v>46272.58123648148</v>
+        <v>46272.60366350695</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="H34" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I34" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J34" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K34" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="L34" s="1">
         <v>46274.125</v>
       </c>
       <c r="M34" s="1">
-        <v>46272.57611934028</v>
+        <v>46272.59989282407</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="H35" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="I35" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J35" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="L35" s="1">
         <v>46274.125</v>
       </c>
       <c r="M35" s="1">
-        <v>46272.559255706015</v>
+        <v>46272.58123648148</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I36" t="s">
         <v>132</v>
       </c>
       <c r="J36" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K36" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="L36" s="1">
         <v>46274.125</v>
       </c>
       <c r="M36" s="1">
-        <v>46272.54757512732</v>
+        <v>46272.57611934028</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -3025,309 +3052,309 @@
         <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
       </c>
       <c r="D37" t="s">
+        <v>134</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" t="s">
         <v>135</v>
       </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>136</v>
       </c>
-      <c r="G37" t="s">
+      <c r="I37" t="s">
         <v>137</v>
       </c>
-      <c r="H37" t="s">
-        <v>138</v>
-      </c>
-      <c r="I37" t="s">
-        <v>19</v>
-      </c>
       <c r="J37" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K37" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="L37" s="1">
         <v>46274.125</v>
       </c>
       <c r="M37" s="1">
-        <v>46272.53882267361</v>
+        <v>46272.559255706015</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
         <v>139</v>
       </c>
-      <c r="B38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" t="s">
+        <v>125</v>
+      </c>
+      <c r="G38" t="s">
         <v>140</v>
       </c>
-      <c r="D38" t="s">
+      <c r="H38" t="s">
         <v>141</v>
       </c>
-      <c r="E38" t="s">
+      <c r="I38" t="s">
         <v>142</v>
       </c>
-      <c r="F38" t="s">
-        <v>143</v>
-      </c>
-      <c r="G38" t="s">
-        <v>144</v>
-      </c>
-      <c r="H38" t="s">
-        <v>145</v>
-      </c>
-      <c r="I38" t="s">
-        <v>19</v>
-      </c>
       <c r="J38" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K38" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="L38" s="1">
-        <v>46271.125</v>
+        <v>46274.125</v>
       </c>
       <c r="M38" s="1">
-        <v>46270.81231954861</v>
+        <v>46272.54757512732</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G39" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H39" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I39" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K39" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="L39" s="1">
-        <v>46272.125</v>
+        <v>46274.125</v>
       </c>
       <c r="M39" s="1">
-        <v>46270.62160388889</v>
+        <v>46272.53882267361</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" t="s">
+        <v>153</v>
+      </c>
+      <c r="H40" t="s">
+        <v>154</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
         <v>155</v>
       </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="K40" t="s">
         <v>156</v>
       </c>
-      <c r="E40" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" t="s">
-        <v>157</v>
-      </c>
-      <c r="G40" t="s">
-        <v>158</v>
-      </c>
-      <c r="H40" t="s">
-        <v>159</v>
-      </c>
-      <c r="I40" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" t="s">
-        <v>160</v>
-      </c>
       <c r="L40" s="1">
-        <v>46270.125</v>
+        <v>46271.125</v>
       </c>
       <c r="M40" s="1">
-        <v>46270.60754677083</v>
+        <v>46270.81231954861</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" t="s">
+        <v>158</v>
+      </c>
+      <c r="E41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G41" t="s">
+        <v>160</v>
+      </c>
+      <c r="H41" t="s">
         <v>161</v>
       </c>
-      <c r="B41" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="I41" t="s">
         <v>162</v>
       </c>
-      <c r="E41" t="s">
-        <v>55</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" t="s">
         <v>163</v>
-      </c>
-      <c r="G41" t="s">
-        <v>164</v>
-      </c>
-      <c r="H41" t="s">
-        <v>165</v>
-      </c>
-      <c r="I41" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" t="s">
-        <v>166</v>
-      </c>
-      <c r="K41" t="s">
-        <v>167</v>
       </c>
       <c r="L41" s="1">
         <v>46272.125</v>
       </c>
       <c r="M41" s="1">
-        <v>46270.58850916667</v>
+        <v>46270.62160388889</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" t="s">
+        <v>166</v>
+      </c>
+      <c r="G42" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" t="s">
         <v>168</v>
       </c>
-      <c r="B42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" t="s">
-        <v>156</v>
-      </c>
-      <c r="E42" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" t="s">
         <v>169</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
-      </c>
-      <c r="H42" t="s">
-        <v>170</v>
-      </c>
-      <c r="I42" t="s">
-        <v>171</v>
-      </c>
-      <c r="J42" t="s">
-        <v>22</v>
-      </c>
-      <c r="K42" t="s">
-        <v>172</v>
       </c>
       <c r="L42" s="1">
         <v>46270.125</v>
       </c>
       <c r="M42" s="1">
-        <v>46269.91888013889</v>
+        <v>46270.60754677083</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
       </c>
       <c r="F43" t="s">
+        <v>172</v>
+      </c>
+      <c r="G43" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" t="s">
         <v>174</v>
       </c>
-      <c r="G43" t="s">
-        <v>19</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
         <v>175</v>
       </c>
-      <c r="I43" t="s">
-        <v>19</v>
-      </c>
-      <c r="J43" t="s">
-        <v>22</v>
-      </c>
       <c r="K43" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="L43" s="1">
-        <v>46269.125</v>
+        <v>46272.125</v>
       </c>
       <c r="M43" s="1">
-        <v>46269.814143993055</v>
+        <v>46270.58850916667</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E44" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F44" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="G44" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="H44" t="s">
         <v>179</v>
@@ -3336,98 +3363,98 @@
         <v>180</v>
       </c>
       <c r="J44" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K44" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="L44" s="1">
-        <v>46269.125</v>
+        <v>46270.125</v>
       </c>
       <c r="M44" s="1">
-        <v>46269.68827564815</v>
+        <v>46269.91888013889</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F45" t="s">
         <v>183</v>
       </c>
       <c r="G45" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" t="s">
         <v>184</v>
       </c>
-      <c r="H45" t="s">
-        <v>185</v>
-      </c>
       <c r="I45" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="J45" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K45" t="s">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="L45" s="1">
-        <v>46271.125</v>
+        <v>46269.125</v>
       </c>
       <c r="M45" s="1">
-        <v>46269.66255648148</v>
+        <v>46269.814143993055</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" t="s">
+        <v>151</v>
+      </c>
+      <c r="F46" t="s">
+        <v>152</v>
+      </c>
+      <c r="G46" t="s">
+        <v>187</v>
+      </c>
+      <c r="H46" t="s">
         <v>188</v>
-      </c>
-      <c r="B46" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" t="s">
-        <v>40</v>
-      </c>
-      <c r="G46" t="s">
-        <v>19</v>
-      </c>
-      <c r="H46" t="s">
-        <v>41</v>
       </c>
       <c r="I46" t="s">
         <v>189</v>
       </c>
       <c r="J46" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="K46" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="L46" s="1">
-        <v>46271.125</v>
+        <v>46269.125</v>
       </c>
       <c r="M46" s="1">
-        <v>46269.55893490741</v>
+        <v>46269.68827564815</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -3435,7 +3462,7 @@
         <v>190</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -3444,154 +3471,154 @@
         <v>191</v>
       </c>
       <c r="E47" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F47" t="s">
         <v>192</v>
       </c>
       <c r="G47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J47" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L47" s="1">
-        <v>46270.125</v>
+        <v>46271.125</v>
       </c>
       <c r="M47" s="1">
-        <v>46268.99017603009</v>
+        <v>46269.66255648148</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F48" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H48" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I48" t="s">
-        <v>42</v>
+        <v>198</v>
       </c>
       <c r="J48" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K48" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L48" s="1">
-        <v>46270.125</v>
+        <v>46271.125</v>
       </c>
       <c r="M48" s="1">
-        <v>46268.79206815972</v>
+        <v>46269.55893490741</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F49" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="H49" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I49" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="K49" t="s">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="L49" s="1">
         <v>46270.125</v>
       </c>
       <c r="M49" s="1">
-        <v>46268.72042950231</v>
+        <v>46268.99017603009</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" t="s">
+        <v>51</v>
+      </c>
+      <c r="G50" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I50" t="s">
         <v>53</v>
       </c>
-      <c r="D50" t="s">
-        <v>177</v>
-      </c>
-      <c r="E50" t="s">
-        <v>142</v>
-      </c>
-      <c r="F50" t="s">
-        <v>199</v>
-      </c>
-      <c r="G50" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" t="s">
-        <v>203</v>
-      </c>
-      <c r="I50" t="s">
-        <v>204</v>
-      </c>
       <c r="J50" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K50" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="L50" s="1">
         <v>46270.125</v>
       </c>
       <c r="M50" s="1">
-        <v>46268.71752466435</v>
+        <v>46268.79206815972</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -3599,286 +3626,286 @@
         <v>206</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F51" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H51" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I51" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J51" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="K51" t="s">
-        <v>205</v>
+        <v>22</v>
       </c>
       <c r="L51" s="1">
         <v>46270.125</v>
       </c>
       <c r="M51" s="1">
-        <v>46268.71495100694</v>
+        <v>46268.72042950231</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>211</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52" t="s">
+        <v>151</v>
+      </c>
+      <c r="F52" t="s">
         <v>208</v>
       </c>
-      <c r="B52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" t="s">
-        <v>177</v>
-      </c>
-      <c r="E52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F52" t="s">
-        <v>199</v>
-      </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H52" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="I52" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J52" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="K52" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="L52" s="1">
         <v>46270.125</v>
       </c>
       <c r="M52" s="1">
-        <v>46268.713350949074</v>
+        <v>46268.71752466435</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F53" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H53" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I53" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J53" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="K53" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="L53" s="1">
         <v>46270.125</v>
       </c>
       <c r="M53" s="1">
-        <v>46268.56635226852</v>
+        <v>46268.71495100694</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F54" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="G54" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" t="s">
+        <v>212</v>
+      </c>
+      <c r="I54" t="s">
+        <v>218</v>
+      </c>
+      <c r="J54" t="s">
+        <v>155</v>
+      </c>
+      <c r="K54" t="s">
         <v>214</v>
-      </c>
-      <c r="H54" t="s">
-        <v>215</v>
-      </c>
-      <c r="I54" t="s">
-        <v>19</v>
-      </c>
-      <c r="J54" t="s">
-        <v>22</v>
-      </c>
-      <c r="K54" t="s">
-        <v>114</v>
       </c>
       <c r="L54" s="1">
         <v>46270.125</v>
       </c>
       <c r="M54" s="1">
-        <v>46268.548608067125</v>
+        <v>46268.713350949074</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
         <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F55" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>220</v>
       </c>
       <c r="I55" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J55" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="K55" t="s">
-        <v>39</v>
+        <v>214</v>
       </c>
       <c r="L55" s="1">
         <v>46270.125</v>
       </c>
       <c r="M55" s="1">
-        <v>46268.53757355324</v>
+        <v>46268.56635226852</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="G56" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H56" t="s">
-        <v>19</v>
+        <v>224</v>
       </c>
       <c r="I56" t="s">
-        <v>222</v>
+        <v>22</v>
       </c>
       <c r="J56" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K56" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="L56" s="1">
-        <v>46267.125</v>
+        <v>46270.125</v>
       </c>
       <c r="M56" s="1">
-        <v>46267.78416134259</v>
+        <v>46268.548608067125</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
         <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F57" t="s">
-        <v>225</v>
+        <v>51</v>
       </c>
       <c r="G57" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="H57" t="s">
-        <v>226</v>
+        <v>52</v>
       </c>
       <c r="I57" t="s">
         <v>227</v>
       </c>
       <c r="J57" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K57" t="s">
-        <v>172</v>
+        <v>50</v>
       </c>
       <c r="L57" s="1">
-        <v>46269.125</v>
+        <v>46270.125</v>
       </c>
       <c r="M57" s="1">
-        <v>46267.65241516204</v>
+        <v>46268.53757355324</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -3886,63 +3913,63 @@
         <v>228</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D58" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" t="s">
         <v>229</v>
       </c>
-      <c r="E58" t="s">
-        <v>142</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>230</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" t="s">
         <v>231</v>
       </c>
-      <c r="H58" t="s">
-        <v>232</v>
-      </c>
-      <c r="I58" t="s">
-        <v>233</v>
-      </c>
       <c r="J58" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K58" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="L58" s="1">
-        <v>46266.125</v>
+        <v>46267.125</v>
       </c>
       <c r="M58" s="1">
-        <v>46265.609358125</v>
+        <v>46267.78416134259</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>232</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>233</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59" t="s">
         <v>234</v>
       </c>
-      <c r="B59" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59" t="s">
-        <v>229</v>
-      </c>
-      <c r="E59" t="s">
-        <v>142</v>
-      </c>
-      <c r="F59" t="s">
-        <v>230</v>
-      </c>
       <c r="G59" t="s">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="H59" t="s">
         <v>235</v>
@@ -3951,16 +3978,16 @@
         <v>236</v>
       </c>
       <c r="J59" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K59" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="L59" s="1">
-        <v>46265.125</v>
+        <v>46269.125</v>
       </c>
       <c r="M59" s="1">
-        <v>46265.60724832176</v>
+        <v>46267.65241516204</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -3968,7 +3995,7 @@
         <v>237</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
         <v>15</v>
@@ -3977,177 +4004,177 @@
         <v>238</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F60" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="G60" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="H60" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I60" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J60" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="K60" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L60" s="1">
         <v>46266.125</v>
       </c>
       <c r="M60" s="1">
-        <v>46264.545438518515</v>
+        <v>46265.609358125</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F61" t="s">
+        <v>239</v>
+      </c>
+      <c r="G61" t="s">
+        <v>240</v>
+      </c>
+      <c r="H61" t="s">
         <v>244</v>
       </c>
-      <c r="G61" t="s">
+      <c r="I61" t="s">
         <v>245</v>
       </c>
-      <c r="H61" t="s">
-        <v>246</v>
-      </c>
-      <c r="I61" t="s">
-        <v>247</v>
-      </c>
       <c r="J61" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="K61" t="s">
-        <v>39</v>
+        <v>238</v>
       </c>
       <c r="L61" s="1">
-        <v>46264.125</v>
+        <v>46265.125</v>
       </c>
       <c r="M61" s="1">
-        <v>46262.64305005787</v>
+        <v>46265.60724832176</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
         <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>182</v>
+        <v>247</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F62" t="s">
+        <v>192</v>
+      </c>
+      <c r="G62" t="s">
+        <v>193</v>
+      </c>
+      <c r="H62" t="s">
+        <v>248</v>
+      </c>
+      <c r="I62" t="s">
         <v>249</v>
       </c>
-      <c r="G62" t="s">
-        <v>101</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="J62" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" t="s">
         <v>250</v>
       </c>
-      <c r="I62" t="s">
-        <v>251</v>
-      </c>
-      <c r="J62" t="s">
-        <v>19</v>
-      </c>
-      <c r="K62" t="s">
-        <v>187</v>
-      </c>
       <c r="L62" s="1">
-        <v>46263.125</v>
+        <v>46266.125</v>
       </c>
       <c r="M62" s="1">
-        <v>46261.88899761574</v>
+        <v>46264.545438518515</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>251</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" t="s">
         <v>252</v>
       </c>
-      <c r="B63" t="s">
-        <v>72</v>
-      </c>
-      <c r="C63" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" t="s">
-        <v>224</v>
-      </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="G63" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J63" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K63" t="s">
-        <v>172</v>
+        <v>50</v>
       </c>
       <c r="L63" s="1">
-        <v>46263.125</v>
+        <v>46264.125</v>
       </c>
       <c r="M63" s="1">
-        <v>46261.847652303244</v>
+        <v>46262.64305005787</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="E64" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="F64" t="s">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="G64" t="s">
-        <v>258</v>
+        <v>111</v>
       </c>
       <c r="H64" t="s">
         <v>259</v>
@@ -4156,16 +4183,16 @@
         <v>260</v>
       </c>
       <c r="J64" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="K64" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="L64" s="1">
         <v>46263.125</v>
       </c>
       <c r="M64" s="1">
-        <v>46261.76887157407</v>
+        <v>46261.88899761574</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -4173,60 +4200,60 @@
         <v>261</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>129</v>
+        <v>233</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="G65" t="s">
-        <v>125</v>
+        <v>262</v>
       </c>
       <c r="H65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J65" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K65" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="L65" s="1">
         <v>46263.125</v>
       </c>
       <c r="M65" s="1">
-        <v>46261.75806057871</v>
+        <v>46261.847652303244</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B66" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E66" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F66" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="G66" t="s">
         <v>267</v>
@@ -4238,16 +4265,16 @@
         <v>269</v>
       </c>
       <c r="J66" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="K66" t="s">
-        <v>19</v>
+        <v>266</v>
       </c>
       <c r="L66" s="1">
-        <v>46262.125</v>
+        <v>46263.125</v>
       </c>
       <c r="M66" s="1">
-        <v>46260.86106256944</v>
+        <v>46261.76887157407</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -4255,227 +4282,227 @@
         <v>270</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
+        <v>139</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" t="s">
+        <v>125</v>
+      </c>
+      <c r="G67" t="s">
+        <v>135</v>
+      </c>
+      <c r="H67" t="s">
         <v>271</v>
       </c>
-      <c r="E67" t="s">
-        <v>142</v>
-      </c>
-      <c r="F67" t="s">
-        <v>199</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="I67" t="s">
         <v>272</v>
       </c>
-      <c r="H67" t="s">
-        <v>273</v>
-      </c>
-      <c r="I67" t="s">
-        <v>274</v>
-      </c>
       <c r="J67" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="K67" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="L67" s="1">
-        <v>46262.125</v>
+        <v>46263.125</v>
       </c>
       <c r="M67" s="1">
-        <v>46260.789700995374</v>
+        <v>46261.75806057871</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E68" t="s">
         <v>17</v>
       </c>
       <c r="F68" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="G68" t="s">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="H68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
       </c>
       <c r="K68" t="s">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="L68" s="1">
         <v>46262.125</v>
       </c>
       <c r="M68" s="1">
-        <v>46260.77278251157</v>
+        <v>46260.86106256944</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E69" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F69" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="G69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H69" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I69" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J69" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="K69" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="L69" s="1">
         <v>46262.125</v>
       </c>
       <c r="M69" s="1">
-        <v>46260.751369895836</v>
+        <v>46260.789700995374</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B70" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>149</v>
+        <v>233</v>
       </c>
       <c r="E70" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F70" t="s">
-        <v>150</v>
+        <v>234</v>
       </c>
       <c r="G70" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="H70" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I70" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J70" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K70" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="L70" s="1">
-        <v>46260.125</v>
+        <v>46262.125</v>
       </c>
       <c r="M70" s="1">
-        <v>46260.68583916667</v>
+        <v>46260.77278251157</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
-        <v>40</v>
+        <v>239</v>
       </c>
       <c r="G71" t="s">
-        <v>101</v>
+        <v>289</v>
       </c>
       <c r="H71" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I71" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J71" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="K71" t="s">
-        <v>39</v>
+        <v>238</v>
       </c>
       <c r="L71" s="1">
         <v>46262.125</v>
       </c>
       <c r="M71" s="1">
-        <v>46260.610648877315</v>
+        <v>46260.751369895836</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
-        <v>279</v>
+        <v>158</v>
       </c>
       <c r="E72" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F72" t="s">
-        <v>291</v>
+        <v>159</v>
       </c>
       <c r="G72" t="s">
-        <v>292</v>
+        <v>111</v>
       </c>
       <c r="H72" t="s">
         <v>293</v>
@@ -4484,39 +4511,39 @@
         <v>294</v>
       </c>
       <c r="J72" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="K72" t="s">
-        <v>295</v>
+        <v>214</v>
       </c>
       <c r="L72" s="1">
-        <v>46262.125</v>
+        <v>46260.125</v>
       </c>
       <c r="M72" s="1">
-        <v>46260.562727013894</v>
+        <v>46260.68583916667</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
       <c r="E73" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F73" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="G73" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H73" t="s">
         <v>297</v>
@@ -4525,16 +4552,16 @@
         <v>298</v>
       </c>
       <c r="J73" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K73" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="L73" s="1">
-        <v>46260.125</v>
+        <v>46262.125</v>
       </c>
       <c r="M73" s="1">
-        <v>46260.553795775464</v>
+        <v>46260.610648877315</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -4542,63 +4569,63 @@
         <v>299</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C74" t="s">
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>149</v>
+        <v>288</v>
       </c>
       <c r="E74" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F74" t="s">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G74" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I74" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J74" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="K74" t="s">
-        <v>205</v>
+        <v>304</v>
       </c>
       <c r="L74" s="1">
-        <v>46261.125</v>
+        <v>46262.125</v>
       </c>
       <c r="M74" s="1">
-        <v>46259.760144201384</v>
+        <v>46260.562727013894</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>304</v>
+        <v>158</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F75" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="G75" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="H75" t="s">
         <v>306</v>
@@ -4607,16 +4634,16 @@
         <v>307</v>
       </c>
       <c r="J75" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="K75" t="s">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="L75" s="1">
         <v>46260.125</v>
       </c>
       <c r="M75" s="1">
-        <v>46258.85121311343</v>
+        <v>46260.553795775464</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -4624,224 +4651,224 @@
         <v>308</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
         <v>15</v>
       </c>
       <c r="D76" t="s">
+        <v>158</v>
+      </c>
+      <c r="E76" t="s">
+        <v>151</v>
+      </c>
+      <c r="F76" t="s">
+        <v>159</v>
+      </c>
+      <c r="G76" t="s">
         <v>309</v>
       </c>
-      <c r="E76" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76" t="s">
-        <v>169</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>310</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>311</v>
       </c>
-      <c r="I76" t="s">
-        <v>312</v>
-      </c>
       <c r="J76" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="K76" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="L76" s="1">
-        <v>46257.125</v>
+        <v>46261.125</v>
       </c>
       <c r="M76" s="1">
-        <v>46255.90268423611</v>
+        <v>46259.760144201384</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>312</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" t="s">
         <v>313</v>
       </c>
-      <c r="B77" t="s">
-        <v>72</v>
-      </c>
-      <c r="C77" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" t="s">
-        <v>177</v>
-      </c>
       <c r="E77" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F77" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G77" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="H77" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I77" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J77" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="K77" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="L77" s="1">
-        <v>46257.125</v>
+        <v>46260.125</v>
       </c>
       <c r="M77" s="1">
-        <v>46255.846485312504</v>
+        <v>46258.85121311343</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E78" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F78" t="s">
-        <v>291</v>
+        <v>178</v>
       </c>
       <c r="G78" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H78" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I78" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J78" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K78" t="s">
-        <v>295</v>
+        <v>181</v>
       </c>
       <c r="L78" s="1">
         <v>46257.125</v>
       </c>
       <c r="M78" s="1">
-        <v>46255.741482881946</v>
+        <v>46255.90268423611</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B79" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>322</v>
+        <v>186</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F79" t="s">
+        <v>208</v>
+      </c>
+      <c r="G79" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" t="s">
         <v>323</v>
       </c>
-      <c r="G79" t="s">
+      <c r="I79" t="s">
         <v>324</v>
       </c>
-      <c r="H79" t="s">
-        <v>325</v>
-      </c>
-      <c r="I79" t="s">
-        <v>326</v>
-      </c>
       <c r="J79" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="K79" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="L79" s="1">
         <v>46257.125</v>
       </c>
       <c r="M79" s="1">
-        <v>46255.72513931713</v>
+        <v>46255.846485312504</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>325</v>
+      </c>
+      <c r="B80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>326</v>
+      </c>
+      <c r="E80" t="s">
+        <v>151</v>
+      </c>
+      <c r="F80" t="s">
+        <v>300</v>
+      </c>
+      <c r="G80" t="s">
         <v>327</v>
       </c>
-      <c r="B80" t="s">
-        <v>72</v>
-      </c>
-      <c r="C80" t="s">
-        <v>24</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="H80" t="s">
+        <v>328</v>
+      </c>
+      <c r="I80" t="s">
+        <v>329</v>
+      </c>
+      <c r="J80" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" t="s">
         <v>304</v>
-      </c>
-      <c r="E80" t="s">
-        <v>17</v>
-      </c>
-      <c r="F80" t="s">
-        <v>183</v>
-      </c>
-      <c r="G80" t="s">
-        <v>328</v>
-      </c>
-      <c r="H80" t="s">
-        <v>329</v>
-      </c>
-      <c r="I80" t="s">
-        <v>330</v>
-      </c>
-      <c r="J80" t="s">
-        <v>19</v>
-      </c>
-      <c r="K80" t="s">
-        <v>160</v>
       </c>
       <c r="L80" s="1">
         <v>46257.125</v>
       </c>
       <c r="M80" s="1">
-        <v>46255.69151269676</v>
+        <v>46255.741482881946</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>330</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>64</v>
+      </c>
+      <c r="D81" t="s">
         <v>331</v>
       </c>
-      <c r="B81" t="s">
-        <v>72</v>
-      </c>
-      <c r="C81" t="s">
-        <v>24</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81" t="s">
         <v>332</v>
-      </c>
-      <c r="E81" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" t="s">
-        <v>183</v>
       </c>
       <c r="G81" t="s">
         <v>333</v>
@@ -4853,16 +4880,16 @@
         <v>335</v>
       </c>
       <c r="J81" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K81" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="L81" s="1">
         <v>46257.125</v>
       </c>
       <c r="M81" s="1">
-        <v>46255.6164808912</v>
+        <v>46255.72513931713</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -4870,183 +4897,183 @@
         <v>336</v>
       </c>
       <c r="B82" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D82" t="s">
-        <v>191</v>
+        <v>313</v>
       </c>
       <c r="E82" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F82" t="s">
         <v>192</v>
       </c>
       <c r="G82" t="s">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="H82" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I82" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J82" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="K82" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="L82" s="1">
         <v>46257.125</v>
       </c>
       <c r="M82" s="1">
-        <v>46255.58180528935</v>
+        <v>46255.69151269676</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E83" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="F83" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="G83" t="s">
-        <v>101</v>
+        <v>342</v>
       </c>
       <c r="H83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I83" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J83" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K83" t="s">
-        <v>265</v>
+        <v>169</v>
       </c>
       <c r="L83" s="1">
-        <v>46255.125</v>
+        <v>46257.125</v>
       </c>
       <c r="M83" s="1">
-        <v>46255.57480164352</v>
+        <v>46255.6164808912</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B84" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>200</v>
       </c>
       <c r="E84" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="F84" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="G84" t="s">
+        <v>201</v>
+      </c>
+      <c r="H84" t="s">
         <v>346</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>347</v>
       </c>
-      <c r="I84" t="s">
-        <v>348</v>
-      </c>
       <c r="J84" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="K84" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="L84" s="1">
         <v>46257.125</v>
       </c>
       <c r="M84" s="1">
-        <v>46255.450155185186</v>
+        <v>46255.58180528935</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>348</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" t="s">
         <v>349</v>
       </c>
-      <c r="B85" t="s">
-        <v>72</v>
-      </c>
-      <c r="C85" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" t="s">
+        <v>77</v>
+      </c>
+      <c r="G85" t="s">
+        <v>111</v>
+      </c>
+      <c r="H85" t="s">
         <v>350</v>
       </c>
-      <c r="E85" t="s">
-        <v>55</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="I85" t="s">
         <v>351</v>
       </c>
-      <c r="G85" t="s">
-        <v>125</v>
-      </c>
-      <c r="H85" t="s">
-        <v>352</v>
-      </c>
-      <c r="I85" t="s">
-        <v>353</v>
-      </c>
       <c r="J85" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K85" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="L85" s="1">
-        <v>46257.125</v>
+        <v>46255.125</v>
       </c>
       <c r="M85" s="1">
-        <v>46255.44403424769</v>
+        <v>46255.57480164352</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B86" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>182</v>
+        <v>353</v>
       </c>
       <c r="E86" t="s">
         <v>17</v>
       </c>
       <c r="F86" t="s">
-        <v>249</v>
+        <v>354</v>
       </c>
       <c r="G86" t="s">
         <v>355</v>
@@ -5058,16 +5085,16 @@
         <v>357</v>
       </c>
       <c r="J86" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="K86" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="L86" s="1">
-        <v>46256.125</v>
+        <v>46257.125</v>
       </c>
       <c r="M86" s="1">
-        <v>46254.83730204861</v>
+        <v>46255.450155185186</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -5075,101 +5102,101 @@
         <v>358</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D87" t="s">
-        <v>304</v>
+        <v>359</v>
       </c>
       <c r="E87" t="s">
         <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>183</v>
+        <v>360</v>
       </c>
       <c r="G87" t="s">
+        <v>135</v>
+      </c>
+      <c r="H87" t="s">
+        <v>361</v>
+      </c>
+      <c r="I87" t="s">
+        <v>362</v>
+      </c>
+      <c r="J87" t="s">
+        <v>22</v>
+      </c>
+      <c r="K87" t="s">
         <v>359</v>
       </c>
-      <c r="H87" t="s">
-        <v>360</v>
-      </c>
-      <c r="I87" t="s">
-        <v>361</v>
-      </c>
-      <c r="J87" t="s">
-        <v>22</v>
-      </c>
-      <c r="K87" t="s">
-        <v>187</v>
-      </c>
       <c r="L87" s="1">
-        <v>46256.125</v>
+        <v>46257.125</v>
       </c>
       <c r="M87" s="1">
-        <v>46254.637882800926</v>
+        <v>46255.44403424769</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B88" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C88" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D88" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F88" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="G88" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H88" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I88" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J88" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K88" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="L88" s="1">
-        <v>46255.125</v>
+        <v>46256.125</v>
       </c>
       <c r="M88" s="1">
-        <v>46253.62513393519</v>
+        <v>46254.83730204861</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D89" t="s">
-        <v>367</v>
+        <v>313</v>
       </c>
       <c r="E89" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F89" t="s">
-        <v>291</v>
+        <v>192</v>
       </c>
       <c r="G89" t="s">
         <v>368</v>
@@ -5181,16 +5208,16 @@
         <v>370</v>
       </c>
       <c r="J89" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K89" t="s">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="L89" s="1">
-        <v>46255.125</v>
+        <v>46256.125</v>
       </c>
       <c r="M89" s="1">
-        <v>46253.58023178241</v>
+        <v>46254.637882800926</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -5198,39 +5225,121 @@
         <v>371</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D90" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="E90" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="F90" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G90" t="s">
-        <v>280</v>
+        <v>372</v>
       </c>
       <c r="H90" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I90" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J90" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K90" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="L90" s="1">
         <v>46255.125</v>
       </c>
       <c r="M90" s="1">
+        <v>46253.62513393519</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>375</v>
+      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s">
+        <v>376</v>
+      </c>
+      <c r="E91" t="s">
+        <v>151</v>
+      </c>
+      <c r="F91" t="s">
+        <v>300</v>
+      </c>
+      <c r="G91" t="s">
+        <v>377</v>
+      </c>
+      <c r="H91" t="s">
+        <v>378</v>
+      </c>
+      <c r="I91" t="s">
+        <v>379</v>
+      </c>
+      <c r="J91" t="s">
+        <v>22</v>
+      </c>
+      <c r="K91" t="s">
+        <v>304</v>
+      </c>
+      <c r="L91" s="1">
+        <v>46255.125</v>
+      </c>
+      <c r="M91" s="1">
+        <v>46253.58023178241</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>380</v>
+      </c>
+      <c r="B92" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="s">
+        <v>353</v>
+      </c>
+      <c r="E92" t="s">
+        <v>151</v>
+      </c>
+      <c r="F92" t="s">
+        <v>239</v>
+      </c>
+      <c r="G92" t="s">
+        <v>289</v>
+      </c>
+      <c r="H92" t="s">
+        <v>381</v>
+      </c>
+      <c r="I92" t="s">
+        <v>382</v>
+      </c>
+      <c r="J92" t="s">
+        <v>22</v>
+      </c>
+      <c r="K92" t="s">
+        <v>22</v>
+      </c>
+      <c r="L92" s="1">
+        <v>46255.125</v>
+      </c>
+      <c r="M92" s="1">
         <v>46253.549469791666</v>
       </c>
     </row>

--- a/Resumo_atividade/Resumo-survey_os_20260908.xlsx
+++ b/Resumo_atividade/Resumo-survey_os_20260908.xlsx
@@ -91,6 +91,12 @@
     <t>Ivan</t>
   </si>
   <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>Prudentópolis</t>
+  </si>
+  <si>
     <t>-25.221782, -51.000775</t>
   </si>
   <si>
@@ -98,12 +104,6 @@
   </si>
   <si>
     <t>OS-2026-0121</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>Prudentópolis</t>
   </si>
   <si>
     <t>Avenida São João</t>
@@ -1667,10 +1667,10 @@
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
         <v>22</v>
@@ -1679,10 +1679,10 @@
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
         <v>25</v>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1708,10 +1708,10 @@
         <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
         <v>22</v>
@@ -1723,7 +1723,7 @@
         <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
         <v>25</v>
@@ -1749,10 +1749,10 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -1764,7 +1764,7 @@
         <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
         <v>25</v>
@@ -1790,10 +1790,10 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
@@ -1805,7 +1805,7 @@
         <v>38</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
         <v>25</v>
@@ -1831,10 +1831,10 @@
         <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
@@ -1846,7 +1846,7 @@
         <v>40</v>
       </c>
       <c r="J7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
@@ -1872,10 +1872,10 @@
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
         <v>22</v>
@@ -1887,7 +1887,7 @@
         <v>42</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K8" t="s">
         <v>25</v>
@@ -1913,10 +1913,10 @@
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
         <v>22</v>
@@ -1928,7 +1928,7 @@
         <v>45</v>
       </c>
       <c r="J9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K9" t="s">
         <v>25</v>
@@ -1954,10 +1954,10 @@
         <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
         <v>22</v>
@@ -1969,7 +1969,7 @@
         <v>47</v>
       </c>
       <c r="J10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K10" t="s">
         <v>25</v>
@@ -1995,7 +1995,7 @@
         <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
         <v>51</v>
@@ -2010,7 +2010,7 @@
         <v>53</v>
       </c>
       <c r="J11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
         <v>50</v>
@@ -2036,10 +2036,10 @@
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
         <v>22</v>
@@ -2051,7 +2051,7 @@
         <v>55</v>
       </c>
       <c r="J12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K12" t="s">
         <v>25</v>
@@ -2077,10 +2077,10 @@
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G13" t="s">
         <v>22</v>
@@ -2092,7 +2092,7 @@
         <v>57</v>
       </c>
       <c r="J13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K13" t="s">
         <v>25</v>
@@ -2118,10 +2118,10 @@
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
         <v>22</v>
@@ -2133,7 +2133,7 @@
         <v>59</v>
       </c>
       <c r="J14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
@@ -2159,10 +2159,10 @@
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
@@ -2174,7 +2174,7 @@
         <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K15" t="s">
         <v>25</v>
@@ -2200,10 +2200,10 @@
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
         <v>22</v>
@@ -2215,7 +2215,7 @@
         <v>61</v>
       </c>
       <c r="J16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -2364,10 +2364,10 @@
         <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
         <v>22</v>
@@ -2379,7 +2379,7 @@
         <v>83</v>
       </c>
       <c r="J20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K20" t="s">
         <v>25</v>
@@ -2405,10 +2405,10 @@
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
         <v>22</v>
@@ -2420,7 +2420,7 @@
         <v>86</v>
       </c>
       <c r="J21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K21" t="s">
         <v>25</v>
@@ -2446,10 +2446,10 @@
         <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
         <v>22</v>
@@ -2461,7 +2461,7 @@
         <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K22" t="s">
         <v>25</v>
@@ -2487,10 +2487,10 @@
         <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
         <v>22</v>
@@ -2502,7 +2502,7 @@
         <v>90</v>
       </c>
       <c r="J23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K23" t="s">
         <v>25</v>
@@ -2528,10 +2528,10 @@
         <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
         <v>22</v>
@@ -2543,7 +2543,7 @@
         <v>93</v>
       </c>
       <c r="J24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K24" t="s">
         <v>25</v>
@@ -2569,10 +2569,10 @@
         <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G25" t="s">
         <v>22</v>
@@ -2584,7 +2584,7 @@
         <v>95</v>
       </c>
       <c r="J25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K25" t="s">
         <v>25</v>
@@ -2610,10 +2610,10 @@
         <v>97</v>
       </c>
       <c r="E26" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F26" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G26" t="s">
         <v>22</v>
@@ -2625,7 +2625,7 @@
         <v>99</v>
       </c>
       <c r="J26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K26" t="s">
         <v>97</v>
@@ -2651,10 +2651,10 @@
         <v>97</v>
       </c>
       <c r="E27" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G27" t="s">
         <v>22</v>
@@ -2666,7 +2666,7 @@
         <v>101</v>
       </c>
       <c r="J27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K27" t="s">
         <v>97</v>
@@ -2692,7 +2692,7 @@
         <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
         <v>105</v>
@@ -2707,7 +2707,7 @@
         <v>108</v>
       </c>
       <c r="J28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K28" t="s">
         <v>109</v>
@@ -2733,7 +2733,7 @@
         <v>104</v>
       </c>
       <c r="E29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>105</v>
@@ -2748,7 +2748,7 @@
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K29" t="s">
         <v>109</v>
@@ -2774,10 +2774,10 @@
         <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G30" t="s">
         <v>22</v>
@@ -2789,7 +2789,7 @@
         <v>115</v>
       </c>
       <c r="J30" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K30" t="s">
         <v>97</v>
@@ -2815,10 +2815,10 @@
         <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G31" t="s">
         <v>22</v>
@@ -2830,7 +2830,7 @@
         <v>117</v>
       </c>
       <c r="J31" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K31" t="s">
         <v>97</v>
@@ -2856,10 +2856,10 @@
         <v>97</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
         <v>22</v>
@@ -2871,7 +2871,7 @@
         <v>119</v>
       </c>
       <c r="J32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K32" t="s">
         <v>97</v>
@@ -2897,10 +2897,10 @@
         <v>97</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
         <v>22</v>
@@ -2912,7 +2912,7 @@
         <v>122</v>
       </c>
       <c r="J33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K33" t="s">
         <v>97</v>
@@ -2938,7 +2938,7 @@
         <v>124</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>125</v>
@@ -2953,7 +2953,7 @@
         <v>128</v>
       </c>
       <c r="J34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K34" t="s">
         <v>124</v>
@@ -2979,10 +2979,10 @@
         <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
         <v>22</v>
@@ -2994,7 +2994,7 @@
         <v>130</v>
       </c>
       <c r="J35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K35" t="s">
         <v>97</v>
@@ -3020,10 +3020,10 @@
         <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G36" t="s">
         <v>22</v>
@@ -3035,7 +3035,7 @@
         <v>132</v>
       </c>
       <c r="J36" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K36" t="s">
         <v>97</v>
@@ -3061,7 +3061,7 @@
         <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
         <v>51</v>
@@ -3076,7 +3076,7 @@
         <v>137</v>
       </c>
       <c r="J37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K37" t="s">
         <v>50</v>
@@ -3102,7 +3102,7 @@
         <v>139</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
         <v>125</v>
@@ -3117,7 +3117,7 @@
         <v>142</v>
       </c>
       <c r="J38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K38" t="s">
         <v>124</v>
@@ -3143,7 +3143,7 @@
         <v>144</v>
       </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F39" t="s">
         <v>145</v>
@@ -3158,7 +3158,7 @@
         <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K39" t="s">
         <v>124</v>
@@ -3266,7 +3266,7 @@
         <v>165</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
         <v>166</v>
@@ -3348,7 +3348,7 @@
         <v>165</v>
       </c>
       <c r="E44" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
         <v>178</v>
@@ -3363,7 +3363,7 @@
         <v>180</v>
       </c>
       <c r="J44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K44" t="s">
         <v>181</v>
@@ -3389,7 +3389,7 @@
         <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F45" t="s">
         <v>183</v>
@@ -3404,7 +3404,7 @@
         <v>22</v>
       </c>
       <c r="J45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K45" t="s">
         <v>109</v>
@@ -3471,7 +3471,7 @@
         <v>191</v>
       </c>
       <c r="E47" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
         <v>192</v>
@@ -3486,7 +3486,7 @@
         <v>195</v>
       </c>
       <c r="J47" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K47" t="s">
         <v>196</v>
@@ -3512,7 +3512,7 @@
         <v>50</v>
       </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F48" t="s">
         <v>51</v>
@@ -3527,7 +3527,7 @@
         <v>198</v>
       </c>
       <c r="J48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K48" t="s">
         <v>50</v>
@@ -3594,7 +3594,7 @@
         <v>50</v>
       </c>
       <c r="E50" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F50" t="s">
         <v>51</v>
@@ -3609,7 +3609,7 @@
         <v>53</v>
       </c>
       <c r="J50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K50" t="s">
         <v>50</v>
@@ -3840,7 +3840,7 @@
         <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F56" t="s">
         <v>145</v>
@@ -3855,7 +3855,7 @@
         <v>22</v>
       </c>
       <c r="J56" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K56" t="s">
         <v>124</v>
@@ -3881,7 +3881,7 @@
         <v>226</v>
       </c>
       <c r="E57" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F57" t="s">
         <v>51</v>
@@ -3896,7 +3896,7 @@
         <v>227</v>
       </c>
       <c r="J57" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K57" t="s">
         <v>50</v>
@@ -3922,7 +3922,7 @@
         <v>165</v>
       </c>
       <c r="E58" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F58" t="s">
         <v>229</v>
@@ -3937,7 +3937,7 @@
         <v>231</v>
       </c>
       <c r="J58" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K58" t="s">
         <v>181</v>
@@ -3963,7 +3963,7 @@
         <v>233</v>
       </c>
       <c r="E59" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F59" t="s">
         <v>234</v>
@@ -3978,7 +3978,7 @@
         <v>236</v>
       </c>
       <c r="J59" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K59" t="s">
         <v>181</v>
@@ -4086,7 +4086,7 @@
         <v>247</v>
       </c>
       <c r="E62" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F62" t="s">
         <v>192</v>
@@ -4127,7 +4127,7 @@
         <v>252</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F63" t="s">
         <v>253</v>
@@ -4142,7 +4142,7 @@
         <v>256</v>
       </c>
       <c r="J63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K63" t="s">
         <v>50</v>
@@ -4168,7 +4168,7 @@
         <v>191</v>
       </c>
       <c r="E64" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F64" t="s">
         <v>258</v>
@@ -4209,7 +4209,7 @@
         <v>233</v>
       </c>
       <c r="E65" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65" t="s">
         <v>234</v>
@@ -4224,7 +4224,7 @@
         <v>264</v>
       </c>
       <c r="J65" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K65" t="s">
         <v>181</v>
@@ -4291,7 +4291,7 @@
         <v>139</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F67" t="s">
         <v>125</v>
@@ -4414,7 +4414,7 @@
         <v>233</v>
       </c>
       <c r="E70" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F70" t="s">
         <v>234</v>
@@ -4429,7 +4429,7 @@
         <v>286</v>
       </c>
       <c r="J70" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K70" t="s">
         <v>181</v>
@@ -4537,7 +4537,7 @@
         <v>296</v>
       </c>
       <c r="E73" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F73" t="s">
         <v>51</v>
@@ -4552,7 +4552,7 @@
         <v>298</v>
       </c>
       <c r="J73" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K73" t="s">
         <v>50</v>
@@ -4701,7 +4701,7 @@
         <v>313</v>
       </c>
       <c r="E77" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77" t="s">
         <v>192</v>
@@ -4742,7 +4742,7 @@
         <v>318</v>
       </c>
       <c r="E78" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F78" t="s">
         <v>178</v>
@@ -4757,7 +4757,7 @@
         <v>321</v>
       </c>
       <c r="J78" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K78" t="s">
         <v>181</v>
@@ -4865,7 +4865,7 @@
         <v>331</v>
       </c>
       <c r="E81" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F81" t="s">
         <v>332</v>
@@ -4880,7 +4880,7 @@
         <v>335</v>
       </c>
       <c r="J81" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K81" t="s">
         <v>50</v>
@@ -4906,7 +4906,7 @@
         <v>313</v>
       </c>
       <c r="E82" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F82" t="s">
         <v>192</v>
@@ -4947,7 +4947,7 @@
         <v>341</v>
       </c>
       <c r="E83" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F83" t="s">
         <v>192</v>
@@ -5152,7 +5152,7 @@
         <v>191</v>
       </c>
       <c r="E88" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F88" t="s">
         <v>258</v>
@@ -5167,7 +5167,7 @@
         <v>366</v>
       </c>
       <c r="J88" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K88" t="s">
         <v>196</v>
@@ -5193,7 +5193,7 @@
         <v>313</v>
       </c>
       <c r="E89" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F89" t="s">
         <v>192</v>
@@ -5208,7 +5208,7 @@
         <v>370</v>
       </c>
       <c r="J89" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K89" t="s">
         <v>196</v>
@@ -5234,7 +5234,7 @@
         <v>233</v>
       </c>
       <c r="E90" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F90" t="s">
         <v>234</v>
@@ -5249,7 +5249,7 @@
         <v>374</v>
       </c>
       <c r="J90" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K90" t="s">
         <v>181</v>
